--- a/artfynd/A 55852-2024 artfynd.xlsx
+++ b/artfynd/A 55852-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97389089</v>
+        <v>99894080</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,57 +686,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stensnäs, Vstm</t>
+          <t>Södra Ås, Nora sn, Vstm 3072 m NE, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502057.5970385191</v>
+        <v>502019</v>
       </c>
       <c r="R2" t="n">
-        <v>6599480.246222723</v>
+        <v>6599108</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,97 +780,78 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Igenväxande inäga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martine Farup</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martine Farup</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97389079</v>
+        <v>99881349</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>100091</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sträckande NO</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stensnäs, Vstm</t>
+          <t>Södra Ås, Nora sn, Vstm 3072 m NE, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502042.336584542</v>
+        <v>502019</v>
       </c>
       <c r="R3" t="n">
-        <v>6599512.699546314</v>
+        <v>6599108</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,93 +899,78 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Igenväxande inäga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martine Farup</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martine Farup</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97389094</v>
+        <v>99881356</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>102952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>sträckande NO</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stensnäs, Vstm</t>
+          <t>Södra Ås, Nora sn, Vstm 3072 m NE, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502083.0216909595</v>
+        <v>502019</v>
       </c>
       <c r="R4" t="n">
-        <v>6599444.247759122</v>
+        <v>6599108</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1037,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,39 +1018,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Igenväxande inäga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martine Farup</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martine Farup</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99894033</v>
+        <v>99894049</v>
       </c>
       <c r="B5" t="n">
-        <v>55946</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102963</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1120,14 +1066,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>sträckande NO</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1137,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502018.6734014118</v>
+        <v>502019</v>
       </c>
       <c r="R5" t="n">
-        <v>6599108.417939438</v>
+        <v>6599108</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1172,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1183,11 +1129,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst. Flockar under morgon och fram till kl. 13:00.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1214,49 +1155,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99894066</v>
+        <v>99894033</v>
       </c>
       <c r="B6" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103037</v>
+        <v>102963</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>sträckande NO</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1266,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502018.6734014118</v>
+        <v>502019</v>
       </c>
       <c r="R6" t="n">
-        <v>6599108.417939438</v>
+        <v>6599108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1301,17 +1237,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-04-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst. Flockar under morgon och fram till kl. 13:00.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,15 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99894039</v>
+        <v>99894057</v>
       </c>
       <c r="B7" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,16 +1290,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102964</v>
+        <v>102987</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1373,14 +1309,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>sträckande NO</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1390,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502018.6734014118</v>
+        <v>502019</v>
       </c>
       <c r="R7" t="n">
-        <v>6599108.417939438</v>
+        <v>6599108</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1425,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1440,7 +1376,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst.</t>
+          <t>Minst</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,49 +1403,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99881349</v>
+        <v>99894066</v>
       </c>
       <c r="B8" t="n">
-        <v>55834</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100091</v>
+        <v>103037</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>sträckande NO</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1519,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502018.6734014118</v>
+        <v>502019</v>
       </c>
       <c r="R8" t="n">
-        <v>6599108.417939438</v>
+        <v>6599108</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1554,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1591,65 +1522,68 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99881356</v>
+        <v>97389079</v>
       </c>
       <c r="B9" t="n">
-        <v>55803</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102952</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>sträckande NO</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Ås, Nora sn, Vstm 3072 m NE, Vstm</t>
+          <t>Stensnäs, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502018.6734014118</v>
+        <v>502043</v>
       </c>
       <c r="R9" t="n">
-        <v>6599108.417939438</v>
+        <v>6599513</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1673,22 +1607,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-04-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-04-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,21 +1621,269 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Igenväxande inäga</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Martine Farup</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Martine Farup</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97389089</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stensnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>502058</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6599480</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Igenväxande inäga</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martine Farup</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Martine Farup</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97389094</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stensnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>502083</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6599445</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Igenväxande inäga</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martine Farup</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martine Farup</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55852-2024 artfynd.xlsx
+++ b/artfynd/A 55852-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99894080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99881349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99881356</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99894049</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1276,6 +1301,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99894033</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,6 +1430,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99894057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1519,6 +1554,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99894066</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97389079</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1765,6 +1810,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97389089</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1884,8 +1934,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97389094</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>